--- a/03_resultados/tablas/tabla_DEGs_completa.xlsx
+++ b/03_resultados/tablas/tabla_DEGs_completa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/09ac1f41c408da74/Escritorio/proyecto_RNA_seq_Los_Simpsons/proyecto_RNASeq_LosSimpsons/03_resultados/tablas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_D15A323800696E75AC88DA1E9FA80093B179CE77" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{666BE9C6-96B7-43DB-A2F4-90A3C166933F}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_D15A323800696E75AC88DA1E9FA80093B179CE77" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47865F8D-BCAD-4C04-95D4-26588423B6B2}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -459,14 +459,14 @@
   <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.77734375" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" customWidth="1"/>
     <col min="2" max="3" width="4.6640625" customWidth="1"/>
     <col min="4" max="4" width="6.6640625" customWidth="1"/>
     <col min="5" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="15.6640625" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" customWidth="1"/>
-    <col min="10" max="10" width="6.6640625" customWidth="1"/>
-    <col min="11" max="11" width="8.6640625" customWidth="1"/>
+    <col min="8" max="8" width="20.44140625" customWidth="1"/>
+    <col min="9" max="9" width="15.88671875" customWidth="1"/>
+    <col min="10" max="10" width="12.109375" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" customWidth="1"/>
     <col min="12" max="12" width="22.77734375" customWidth="1"/>
   </cols>
   <sheetData>
